--- a/Web crawling/Review/reviews_by_store/S016.xlsx
+++ b/Web crawling/Review/reviews_by_store/S016.xlsx
@@ -46,8 +46,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K801"/>
+  <dimension ref="A1:K808"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43891,6 +43894,393 @@
         </is>
       </c>
     </row>
+    <row r="802">
+      <c r="A802" s="1" t="inlineStr">
+        <is>
+          <t>S016-0801</t>
+        </is>
+      </c>
+      <c r="B802" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="C802" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="D802" s="1" t="inlineStr">
+        <is>
+          <t>602753b5a896272d5c0ef7eb</t>
+        </is>
+      </c>
+      <c r="E802" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F802" s="1" t="inlineStr">
+        <is>
+          <t>점심</t>
+        </is>
+      </c>
+      <c r="G802" s="1" t="inlineStr">
+        <is>
+          <t>바로 입장</t>
+        </is>
+      </c>
+      <c r="H802" s="1" t="inlineStr">
+        <is>
+          <t>예약 없이 이용, 친목, 기념일, 지인・동료</t>
+        </is>
+      </c>
+      <c r="I802" s="1" t="inlineStr">
+        <is>
+          <t>몽글몽글하고 폭신한 수플레 팬케이크 맛집입니다. 브런치 조합도 훌륭해서 식사 겸 디저트로 즐기기 딱 좋았어요. 재료도 신선하고 전체적인 간이나 밸런스가 뛰어나 만족스럽게 먹었습니다. 꼭 들러보세요.</t>
+        </is>
+      </c>
+      <c r="J802" s="1" t="inlineStr">
+        <is>
+          <t>8.25.화</t>
+        </is>
+      </c>
+      <c r="K802" s="1" t="inlineStr">
+        <is>
+          <t>1번째 방문</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="1" t="inlineStr">
+        <is>
+          <t>S016-0802</t>
+        </is>
+      </c>
+      <c r="B803" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="C803" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="D803" s="1" t="inlineStr">
+        <is>
+          <t>675cfe2773736e3dcfc8fd38</t>
+        </is>
+      </c>
+      <c r="E803" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F803" s="1" t="inlineStr">
+        <is>
+          <t>저녁</t>
+        </is>
+      </c>
+      <c r="G803" s="1" t="inlineStr">
+        <is>
+          <t>바로 입장</t>
+        </is>
+      </c>
+      <c r="H803" s="1" t="inlineStr">
+        <is>
+          <t>예약 없이 이용, 데이트, 연인・배우자</t>
+        </is>
+      </c>
+      <c r="I803" s="1" t="inlineStr">
+        <is>
+          <t>수플레 맛집 야르!!!!</t>
+        </is>
+      </c>
+      <c r="J803" s="1" t="inlineStr">
+        <is>
+          <t>8.24.월</t>
+        </is>
+      </c>
+      <c r="K803" s="1" t="inlineStr">
+        <is>
+          <t>1번째 방문</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="1" t="inlineStr">
+        <is>
+          <t>S016-0803</t>
+        </is>
+      </c>
+      <c r="B804" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="C804" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="D804" s="1" t="inlineStr">
+        <is>
+          <t>60ad80d8102e487157d9cf67</t>
+        </is>
+      </c>
+      <c r="E804" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F804" s="1" t="inlineStr">
+        <is>
+          <t>점심</t>
+        </is>
+      </c>
+      <c r="G804" s="1" t="inlineStr">
+        <is>
+          <t>바로 입장</t>
+        </is>
+      </c>
+      <c r="H804" s="1" t="inlineStr">
+        <is>
+          <t>예약 없이 이용, 데이트, 연인・배우자, 친구</t>
+        </is>
+      </c>
+      <c r="I804" s="1" t="inlineStr">
+        <is>
+          <t>신기한 디저트가 많고 맛있어용~ 친구들이랑 같이 오기 좋은 카페에용~ 콘센트가 잘 구비되어 있어, 대화하기에도 좋아요 만족스러워요</t>
+        </is>
+      </c>
+      <c r="J804" s="1" t="inlineStr">
+        <is>
+          <t>8.24.월</t>
+        </is>
+      </c>
+      <c r="K804" s="1" t="inlineStr">
+        <is>
+          <t>1번째 방문</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="1" t="inlineStr">
+        <is>
+          <t>S016-0804</t>
+        </is>
+      </c>
+      <c r="B805" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="C805" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="D805" s="1" t="inlineStr">
+        <is>
+          <t>5dc892988f87a842bc5494c8</t>
+        </is>
+      </c>
+      <c r="E805" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F805" s="1" t="inlineStr">
+        <is>
+          <t>점심</t>
+        </is>
+      </c>
+      <c r="G805" s="1" t="inlineStr">
+        <is>
+          <t>바로 입장</t>
+        </is>
+      </c>
+      <c r="H805" s="1" t="inlineStr">
+        <is>
+          <t>예약 없이 이용, 친목, 친구</t>
+        </is>
+      </c>
+      <c r="I805" s="1" t="inlineStr">
+        <is>
+          <t>디저트가 너무 맛있고 수플레 진짜진짜 맛있어요!! 자리도 넓고 쾌적하니 너무 좋네용</t>
+        </is>
+      </c>
+      <c r="J805" s="1" t="inlineStr">
+        <is>
+          <t>8.23.일</t>
+        </is>
+      </c>
+      <c r="K805" s="1" t="inlineStr">
+        <is>
+          <t>1번째 방문</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="1" t="inlineStr">
+        <is>
+          <t>S016-0805</t>
+        </is>
+      </c>
+      <c r="B806" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="C806" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="D806" s="1" t="inlineStr">
+        <is>
+          <t>5d9c0f178f87a842bcf47a33</t>
+        </is>
+      </c>
+      <c r="E806" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F806" s="1" t="inlineStr">
+        <is>
+          <t>점심</t>
+        </is>
+      </c>
+      <c r="G806" s="1" t="inlineStr">
+        <is>
+          <t>바로 입장</t>
+        </is>
+      </c>
+      <c r="H806" s="1" t="inlineStr">
+        <is>
+          <t>예약 없이 이용, 친목, 친구</t>
+        </is>
+      </c>
+      <c r="I806" s="1" t="inlineStr">
+        <is>
+          <t>인터넷에서 보다가 처음 방문해 봤는데 메뉴도 다양하고 맛도 맛있어서 좋았어요! 알바생 분도 친절해요!!!</t>
+        </is>
+      </c>
+      <c r="J806" s="1" t="inlineStr">
+        <is>
+          <t>8.22.토</t>
+        </is>
+      </c>
+      <c r="K806" s="1" t="inlineStr">
+        <is>
+          <t>1번째 방문</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="1" t="inlineStr">
+        <is>
+          <t>S016-0806</t>
+        </is>
+      </c>
+      <c r="B807" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="C807" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="D807" s="1" t="inlineStr">
+        <is>
+          <t>5eff5d1ede5d1e6a342ab754</t>
+        </is>
+      </c>
+      <c r="E807" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F807" s="1" t="inlineStr">
+        <is>
+          <t>점심</t>
+        </is>
+      </c>
+      <c r="G807" s="1" t="inlineStr">
+        <is>
+          <t>바로 입장</t>
+        </is>
+      </c>
+      <c r="H807" s="1" t="inlineStr">
+        <is>
+          <t>예약 없이 이용, 데이트, 연인・배우자</t>
+        </is>
+      </c>
+      <c r="I807" s="1" t="inlineStr">
+        <is>
+          <t>너무 부드럽고 맛있어요</t>
+        </is>
+      </c>
+      <c r="J807" s="1" t="inlineStr">
+        <is>
+          <t>8.22.토</t>
+        </is>
+      </c>
+      <c r="K807" s="1" t="inlineStr">
+        <is>
+          <t>1번째 방문</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="1" t="inlineStr">
+        <is>
+          <t>S016-0807</t>
+        </is>
+      </c>
+      <c r="B808" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="C808" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="D808" s="1" t="inlineStr">
+        <is>
+          <t>60f67e994b77c229801eb56e</t>
+        </is>
+      </c>
+      <c r="E808" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F808" s="1" t="inlineStr">
+        <is>
+          <t>점심</t>
+        </is>
+      </c>
+      <c r="G808" s="1" t="inlineStr">
+        <is>
+          <t>바로 입장</t>
+        </is>
+      </c>
+      <c r="H808" s="1" t="inlineStr">
+        <is>
+          <t>예약 없이 이용, 데이트, 연인・배우자</t>
+        </is>
+      </c>
+      <c r="I808" s="1" t="inlineStr">
+        <is>
+          <t>가격대비 괜찮은것갗아요
+맛있음
+예쁨</t>
+        </is>
+      </c>
+      <c r="J808" s="1" t="inlineStr">
+        <is>
+          <t>8.20.목</t>
+        </is>
+      </c>
+      <c r="K808" s="1" t="inlineStr">
+        <is>
+          <t>1번째 방문</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
